--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="424">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -274,6 +274,9 @@
     <t>Organization(classCode=ORG, determinerCode=INST)</t>
   </si>
   <si>
+    <t>administrative.group</t>
+  </si>
+  <si>
     <t>Organization.id</t>
   </si>
   <si>
@@ -357,7 +360,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -415,6 +418,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -462,6 +469,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Organization.modifierExtension</t>
   </si>
   <si>
@@ -479,7 +490,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -539,201 +550,195 @@
     <t>Organization.identifier.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.version</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.version</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.version</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -915,7 +920,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1202,6 +1207,10 @@
   </si>
   <si>
     <t>Need to keep track of assigned contact points within bigger organization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>.contactParty</t>
@@ -1666,7 +1675,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.10546875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1914,15 +1923,15 @@
         <v>30</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1933,7 +1942,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -1942,19 +1951,19 @@
         <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2004,13 +2013,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2033,10 +2042,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2047,7 +2056,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>77</v>
@@ -2056,16 +2065,16 @@
         <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2116,19 +2125,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2145,10 +2154,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2159,28 +2168,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2230,19 +2239,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2259,10 +2268,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2273,7 +2282,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2285,16 +2294,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2320,13 +2329,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2344,19 +2353,19 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2373,21 +2382,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2399,16 +2408,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2458,25 +2467,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2487,14 +2496,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2513,16 +2522,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2572,7 +2581,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2584,13 +2593,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2601,10 +2610,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2612,7 +2621,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2627,13 +2636,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2672,17 +2681,17 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2694,7 +2703,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2711,23 +2720,23 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>77</v>
@@ -2739,13 +2748,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>9</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2796,7 +2805,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2805,10 +2814,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2825,14 +2834,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2845,25 +2854,25 @@
         <v>77</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2912,7 +2921,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2924,13 +2933,13 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2941,10 +2950,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2952,7 +2961,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>79</v>
@@ -2964,20 +2973,20 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3014,19 +3023,19 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3035,33 +3044,33 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
@@ -3071,29 +3080,29 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3142,7 +3151,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3151,30 +3160,30 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3185,7 +3194,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
@@ -3197,13 +3206,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3254,13 +3263,13 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
@@ -3272,7 +3281,7 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3283,14 +3292,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3309,16 +3318,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3356,19 +3365,19 @@
         <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3380,13 +3389,13 @@
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3397,10 +3406,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3411,31 +3420,31 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3460,13 +3469,11 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3484,25 +3491,25 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3513,10 +3520,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3527,7 +3534,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3536,22 +3543,22 @@
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3576,11 +3583,9 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="Y17" t="s" s="2">
         <v>197</v>
       </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
         <v>198</v>
       </c>
@@ -3606,19 +3611,19 @@
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>200</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3643,7 +3648,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -3655,13 +3660,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3712,13 +3717,13 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
@@ -3730,7 +3735,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3748,7 +3753,7 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3767,16 +3772,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3814,19 +3819,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3838,13 +3843,13 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3878,7 +3883,7 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>207</v>
@@ -3954,7 +3959,7 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>213</v>
@@ -3985,7 +3990,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -3997,13 +4002,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4054,13 +4059,13 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
@@ -4072,7 +4077,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4090,7 +4095,7 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4109,16 +4114,16 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4156,19 +4161,19 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4180,13 +4185,13 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4211,7 +4216,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4220,10 +4225,10 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>221</v>
@@ -4290,13 +4295,13 @@
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>227</v>
@@ -4327,7 +4332,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4336,19 +4341,19 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4398,25 +4403,25 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4427,10 +4432,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4441,7 +4446,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4450,20 +4455,20 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4473,7 +4478,7 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>77</v>
@@ -4512,25 +4517,25 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4541,10 +4546,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4555,7 +4560,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4564,20 +4569,20 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4587,7 +4592,7 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>77</v>
@@ -4626,25 +4631,25 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4655,10 +4660,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4669,7 +4674,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4678,22 +4683,22 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4742,25 +4747,25 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4771,10 +4776,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4785,7 +4790,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4794,22 +4799,22 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4819,7 +4824,7 @@
         <v>77</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>77</v>
@@ -4858,25 +4863,25 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4887,10 +4892,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4898,10 +4903,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4910,35 +4915,35 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>77</v>
@@ -4974,28 +4979,28 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5003,10 +5008,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5017,28 +5022,28 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5052,7 +5057,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5088,28 +5093,28 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5117,10 +5122,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5131,7 +5136,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5140,16 +5145,16 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5200,28 +5205,28 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5229,10 +5234,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5243,7 +5248,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5252,19 +5257,19 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5314,28 +5319,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5343,10 +5348,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5357,114 +5362,114 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I33" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q33" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="R33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH33" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="J33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="P33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q33" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="R33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5484,22 +5489,22 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5524,13 +5529,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5548,7 +5553,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5560,27 +5565,27 @@
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5588,10 +5593,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5600,22 +5605,22 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5664,28 +5669,28 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5693,10 +5698,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5719,19 +5724,19 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5780,7 +5785,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5792,13 +5797,13 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5809,10 +5814,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5835,19 +5840,19 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5896,7 +5901,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5905,19 +5910,19 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5925,10 +5930,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5951,19 +5956,19 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6012,7 +6017,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6021,19 +6026,19 @@
         <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6041,10 +6046,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6055,7 +6060,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -6064,20 +6069,20 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6126,28 +6131,28 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6155,10 +6160,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6181,19 +6186,19 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6242,7 +6247,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6254,13 +6259,13 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>384</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6271,10 +6276,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6285,7 +6290,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6297,13 +6302,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6354,13 +6359,13 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
@@ -6372,7 +6377,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6383,14 +6388,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6409,16 +6414,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6468,7 +6473,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6480,13 +6485,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6497,14 +6502,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6517,25 +6522,25 @@
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6584,7 +6589,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6596,13 +6601,13 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6613,10 +6618,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6627,7 +6632,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6639,17 +6644,17 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6674,13 +6679,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6698,25 +6703,25 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6727,10 +6732,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6741,7 +6746,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6753,17 +6758,17 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6812,25 +6817,25 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6841,10 +6846,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6867,17 +6872,17 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6926,7 +6931,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6938,13 +6943,13 @@
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6955,10 +6960,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6969,7 +6974,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6981,17 +6986,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7040,25 +7045,25 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7069,10 +7074,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7095,17 +7100,17 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7154,7 +7159,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7166,13 +7171,13 @@
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="422">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -274,9 +274,6 @@
     <t>Organization(classCode=ORG, determinerCode=INST)</t>
   </si>
   <si>
-    <t>administrative.group</t>
-  </si>
-  <si>
     <t>Organization.id</t>
   </si>
   <si>
@@ -360,7 +357,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -418,10 +415,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -469,10 +462,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>Organization.modifierExtension</t>
   </si>
   <si>
@@ -490,7 +479,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -550,6 +539,10 @@
     <t>Organization.identifier.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -601,7 +594,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -635,6 +631,9 @@
     <t>extensible</t>
   </si>
   <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
@@ -735,10 +734,6 @@
     <t>Organization.identifier.type.coding.version</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -920,7 +915,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1207,10 +1202,6 @@
   </si>
   <si>
     <t>Need to keep track of assigned contact points within bigger organization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>.contactParty</t>
@@ -1675,7 +1666,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.10546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1923,15 +1914,15 @@
         <v>30</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1942,28 +1933,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2013,13 +2004,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2042,10 +2033,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2056,25 +2047,25 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2125,19 +2116,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2154,10 +2145,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2168,28 +2159,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2239,19 +2230,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2268,10 +2259,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2282,7 +2273,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2294,16 +2285,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2329,43 +2320,43 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2382,21 +2373,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2408,16 +2399,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2467,25 +2458,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2496,14 +2487,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2522,16 +2513,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2581,7 +2572,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2593,13 +2584,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2610,10 +2601,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2621,7 +2612,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2636,13 +2627,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2681,17 +2672,17 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2703,7 +2694,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2720,23 +2711,23 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>77</v>
@@ -2748,13 +2739,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>9</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2805,7 +2796,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2814,10 +2805,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2834,14 +2825,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2854,25 +2845,25 @@
         <v>77</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="O11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2921,7 +2912,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2933,13 +2924,13 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2950,10 +2941,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2961,7 +2952,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>79</v>
@@ -2973,20 +2964,20 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3023,19 +3014,19 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3044,33 +3035,33 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>165</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
@@ -3080,29 +3071,29 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H13" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H13" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3151,7 +3142,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3160,30 +3151,30 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>165</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3194,7 +3185,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
@@ -3206,13 +3197,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3263,13 +3254,13 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
@@ -3281,7 +3272,7 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3292,14 +3283,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3318,16 +3309,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3365,19 +3356,19 @@
         <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3389,13 +3380,13 @@
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3406,10 +3397,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3420,31 +3411,31 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I16" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3469,47 +3460,49 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y16" s="2"/>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3520,10 +3513,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3534,31 +3527,31 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3583,9 +3576,11 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
         <v>198</v>
       </c>
@@ -3611,19 +3606,19 @@
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>200</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3648,7 +3643,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -3660,13 +3655,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3717,13 +3712,13 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
@@ -3735,7 +3730,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3753,7 +3748,7 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3772,16 +3767,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3819,19 +3814,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3843,13 +3838,13 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3883,7 +3878,7 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>207</v>
@@ -3959,7 +3954,7 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>213</v>
@@ -3990,7 +3985,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -4002,13 +3997,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4059,13 +4054,13 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
@@ -4077,7 +4072,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4095,7 +4090,7 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4114,16 +4109,16 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4161,19 +4156,19 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4185,13 +4180,13 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4216,19 +4211,19 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K23" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>221</v>
@@ -4295,13 +4290,13 @@
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>227</v>
@@ -4332,28 +4327,28 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K24" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4403,25 +4398,25 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK24" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK24" t="s" s="2">
+      <c r="AL24" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4432,10 +4427,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4446,29 +4441,29 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4478,64 +4473,64 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="T25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF25" t="s" s="2">
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AG25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AL25" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4546,10 +4541,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4560,29 +4555,29 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K26" t="s" s="2">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4592,64 +4587,64 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="T26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF26" t="s" s="2">
+      <c r="AG26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AL26" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4660,10 +4655,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4674,31 +4669,31 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K27" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4747,25 +4742,25 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4776,10 +4771,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4790,31 +4785,31 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4824,64 +4819,64 @@
         <v>77</v>
       </c>
       <c r="S28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="T28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF28" t="s" s="2">
+      <c r="AG28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AL28" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4892,10 +4887,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4903,104 +4898,104 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G29" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T29" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="S29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T29" t="s" s="2">
+      <c r="U29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="U29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
+      <c r="AG29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK29" t="s" s="2">
+      <c r="AL29" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5008,10 +5003,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5022,28 +5017,28 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H30" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H30" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5057,64 +5052,64 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="U30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK30" t="s" s="2">
+      <c r="AL30" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5122,10 +5117,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5136,25 +5131,25 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5205,28 +5200,28 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5234,10 +5229,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5248,28 +5243,28 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K32" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5319,28 +5314,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AG32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK32" t="s" s="2">
+      <c r="AL32" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5348,10 +5343,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5362,114 +5357,114 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="O33" t="s" s="2">
+      <c r="P33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q33" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="P33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q33" t="s" s="2">
+      <c r="R33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK33" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="R33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK33" t="s" s="2">
+      <c r="AL33" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>326</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5489,22 +5484,22 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5529,14 +5524,14 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="Y34" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="Y34" t="s" s="2">
+      <c r="Z34" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5553,7 +5548,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5565,27 +5560,27 @@
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5593,34 +5588,34 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5669,28 +5664,28 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5698,10 +5693,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5724,19 +5719,19 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5785,7 +5780,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5797,13 +5792,13 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5814,10 +5809,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5840,19 +5835,19 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5901,7 +5896,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5910,19 +5905,19 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AJ37" t="s" s="2">
+      <c r="AK37" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AK37" t="s" s="2">
+      <c r="AL37" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5930,10 +5925,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5956,19 +5951,19 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6017,7 +6012,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6026,19 +6021,19 @@
         <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AJ38" t="s" s="2">
+      <c r="AK38" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AK38" t="s" s="2">
+      <c r="AL38" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6046,10 +6041,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6060,29 +6055,29 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J39" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K39" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6131,28 +6126,28 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6160,10 +6155,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6186,19 +6181,19 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6247,7 +6242,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6259,13 +6254,13 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>384</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6276,10 +6271,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6290,7 +6285,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6302,13 +6297,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6359,13 +6354,13 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
@@ -6377,7 +6372,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6388,14 +6383,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6414,16 +6409,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6473,7 +6468,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6485,13 +6480,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6502,14 +6497,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6522,25 +6517,25 @@
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6589,7 +6584,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6601,13 +6596,13 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6618,10 +6613,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6632,7 +6627,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6644,17 +6639,17 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6679,49 +6674,49 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6732,10 +6727,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6746,7 +6741,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6758,17 +6753,17 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6817,25 +6812,25 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6846,10 +6841,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6872,17 +6867,17 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6931,7 +6926,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6943,13 +6938,13 @@
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6960,10 +6955,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6974,7 +6969,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6986,17 +6981,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7045,25 +7040,25 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7074,10 +7069,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7100,17 +7095,17 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7159,7 +7154,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7171,13 +7166,13 @@
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-implementing-partner.xlsx
+++ b/branches/Richard/StructureDefinition-implementing-partner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
